--- a/artfynd/A 43507-2023 artfynd.xlsx
+++ b/artfynd/A 43507-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117766428</v>
+        <v>117766421</v>
       </c>
       <c r="B2" t="n">
-        <v>100070</v>
+        <v>104914</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1365</v>
+        <v>221725</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>763231</v>
+        <v>763297</v>
       </c>
       <c r="R2" t="n">
-        <v>7341583</v>
+        <v>7341600</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117766430</v>
+        <v>117766225</v>
       </c>
       <c r="B3" t="n">
-        <v>95131</v>
+        <v>100070</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>763241</v>
+        <v>763227</v>
       </c>
       <c r="R3" t="n">
-        <v>7341571</v>
+        <v>7341580</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117766421</v>
+        <v>117766419</v>
       </c>
       <c r="B4" t="n">
-        <v>104914</v>
+        <v>95131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221725</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>763297</v>
+        <v>763233</v>
       </c>
       <c r="R4" t="n">
-        <v>7341600</v>
+        <v>7341585</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117766225</v>
+        <v>117766430</v>
       </c>
       <c r="B5" t="n">
-        <v>100070</v>
+        <v>95131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>763227</v>
+        <v>763241</v>
       </c>
       <c r="R5" t="n">
-        <v>7341580</v>
+        <v>7341571</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117766419</v>
+        <v>117766428</v>
       </c>
       <c r="B6" t="n">
-        <v>95131</v>
+        <v>100070</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>763233</v>
+        <v>763231</v>
       </c>
       <c r="R6" t="n">
-        <v>7341585</v>
+        <v>7341583</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 43507-2023 artfynd.xlsx
+++ b/artfynd/A 43507-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117766421</v>
+        <v>117766428</v>
       </c>
       <c r="B2" t="n">
-        <v>104914</v>
+        <v>100072</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>1365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>763297</v>
+        <v>763231</v>
       </c>
       <c r="R2" t="n">
-        <v>7341600</v>
+        <v>7341583</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117766225</v>
+        <v>117766419</v>
       </c>
       <c r="B3" t="n">
-        <v>100070</v>
+        <v>95133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>763227</v>
+        <v>763233</v>
       </c>
       <c r="R3" t="n">
-        <v>7341580</v>
+        <v>7341585</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117766419</v>
+        <v>117766421</v>
       </c>
       <c r="B4" t="n">
-        <v>95131</v>
+        <v>104916</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>221725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>763233</v>
+        <v>763297</v>
       </c>
       <c r="R4" t="n">
-        <v>7341585</v>
+        <v>7341600</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,7 +1011,7 @@
         <v>117766430</v>
       </c>
       <c r="B5" t="n">
-        <v>95131</v>
+        <v>95133</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117766428</v>
+        <v>117766225</v>
       </c>
       <c r="B6" t="n">
-        <v>100070</v>
+        <v>100072</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>763231</v>
+        <v>763227</v>
       </c>
       <c r="R6" t="n">
-        <v>7341583</v>
+        <v>7341580</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
